--- a/IDR_Template.xlsx
+++ b/IDR_Template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDR_Form" sheetId="1" r:id="R9506cacede5a4638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDOT_Pay_Items" sheetId="2" r:id="R3ff968863502494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDR_Form" sheetId="1" r:id="R6734295c17f34406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDOT_Pay_Items" sheetId="2" r:id="R20ec1be5239c4146"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="PayItemNumbers">#REF!</x:definedName>
@@ -171,12 +171,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="D9EAF7"/>
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2CC"/>
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -186,230 +186,230 @@
     <x:border/>
     <x:border>
       <x:left style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:bottom style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border/>
     <x:border>
       <x:left style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:left>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:bottom style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:right style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="medium">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="000000"/>
+        <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="75">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -571,6 +571,64 @@
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -718,13 +776,13 @@
     <xdr:ext cx="2095500" cy="581025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image1.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R067f218d09504003"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2abb7ec6cb5f419f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1038,7 +1096,7 @@
       </x:c>
       <x:c r="C6" s="27" t="n">
         <x:f>TODAY()</x:f>
-        <x:v>46174</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="D6" s="26"/>
       <x:c r="E6" s="1"/>
@@ -1198,7 +1256,9 @@
     </x:row>
     <x:row r="13" ht="33.95000076293945" customHeight="1">
       <x:c r="A13" s="1"/>
-      <x:c r="B13" s="6"/>
+      <x:c r="B13" s="6" t="str">
+        <x:f>IF($D13="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D13,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C13" s="7"/>
       <x:c r="D13" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B13,#REF!,2,FALSE),"")</x:f>
@@ -1210,7 +1270,7 @@
         <x:f>IF($B13&lt;&gt;"",IFERROR(VLOOKUP($B13,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B13,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D13&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D13,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D13,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I13" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B13,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D13="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D13,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J13" s="16"/>
       <x:c r="K13" s="31"/>
@@ -1226,7 +1286,9 @@
     </x:row>
     <x:row r="14" ht="33.95000076293945" customHeight="1">
       <x:c r="A14" s="1"/>
-      <x:c r="B14" s="6"/>
+      <x:c r="B14" s="6" t="str">
+        <x:f>IF($D14="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D14,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C14" s="7"/>
       <x:c r="D14" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B14,#REF!,2,FALSE),"")</x:f>
@@ -1238,7 +1300,7 @@
         <x:f>IF($B14&lt;&gt;"",IFERROR(VLOOKUP($B14,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B14,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D14&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D14,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D14,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I14" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B14,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D14="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D14,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J14" s="16"/>
       <x:c r="K14" s="31"/>
@@ -1254,7 +1316,9 @@
     </x:row>
     <x:row r="15" ht="33.95000076293945" customHeight="1">
       <x:c r="A15" s="1"/>
-      <x:c r="B15" s="6"/>
+      <x:c r="B15" s="6" t="str">
+        <x:f>IF($D15="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D15,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C15" s="7"/>
       <x:c r="D15" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B15,#REF!,2,FALSE),"")</x:f>
@@ -1266,7 +1330,7 @@
         <x:f>IF($B15&lt;&gt;"",IFERROR(VLOOKUP($B15,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B15,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D15&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D15,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D15,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I15" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B15,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D15="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D15,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J15" s="16"/>
       <x:c r="K15" s="31"/>
@@ -1282,7 +1346,9 @@
     </x:row>
     <x:row r="16" ht="33.95000076293945" customHeight="1">
       <x:c r="A16" s="1"/>
-      <x:c r="B16" s="6"/>
+      <x:c r="B16" s="6" t="str">
+        <x:f>IF($D16="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D16,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C16" s="7"/>
       <x:c r="D16" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B16,#REF!,2,FALSE),"")</x:f>
@@ -1294,7 +1360,7 @@
         <x:f>IF($B16&lt;&gt;"",IFERROR(VLOOKUP($B16,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B16,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D16&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D16,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D16,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I16" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B16,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D16="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D16,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J16" s="16"/>
       <x:c r="K16" s="31"/>
@@ -1310,7 +1376,9 @@
     </x:row>
     <x:row r="17" ht="33.95000076293945" customHeight="1">
       <x:c r="A17" s="1"/>
-      <x:c r="B17" s="6"/>
+      <x:c r="B17" s="6" t="str">
+        <x:f>IF($D17="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D17,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C17" s="7"/>
       <x:c r="D17" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B17,#REF!,2,FALSE),"")</x:f>
@@ -1322,7 +1390,7 @@
         <x:f>IF($B17&lt;&gt;"",IFERROR(VLOOKUP($B17,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B17,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D17&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D17,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D17,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I17" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B17,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D17="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D17,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J17" s="16"/>
       <x:c r="K17" s="31"/>
@@ -1338,7 +1406,9 @@
     </x:row>
     <x:row r="18" ht="33.95000076293945" customHeight="1">
       <x:c r="A18" s="1"/>
-      <x:c r="B18" s="6"/>
+      <x:c r="B18" s="6" t="str">
+        <x:f>IF($D18="","",IFERROR(INDEX(IDOT_Pay_Items!$A:$A,MATCH($D18,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
+      </x:c>
       <x:c r="C18" s="7"/>
       <x:c r="D18" s="18" t="str">
         <x:f>IFERROR(VLOOKUP(B18,#REF!,2,FALSE),"")</x:f>
@@ -1350,7 +1420,7 @@
         <x:f>IF($B18&lt;&gt;"",IFERROR(VLOOKUP($B18,IDOT_Pay_Items!$A$2:$E$501,4,FALSE)&amp;" "&amp;VLOOKUP($B18,IDOT_Pay_Items!$A$2:$E$501,2,FALSE),""),IF($D18&lt;&gt;"",IFERROR(INDEX(IDOT_Pay_Items!$D$2:$D$501,MATCH($D18,IDOT_Pay_Items!$C$2:$C$501,0))&amp;" "&amp;INDEX(IDOT_Pay_Items!$B$2:$B$501,MATCH($D18,IDOT_Pay_Items!$C$2:$C$501,0)),""),""))</x:f>
       </x:c>
       <x:c r="I18" s="9" t="str">
-        <x:f>IFERROR(VLOOKUP(B18,#REF!,3,FALSE),"")</x:f>
+        <x:f>IF($D18="","",IFERROR(INDEX(IDOT_Pay_Items!$B:$B,MATCH($D18,IDOT_Pay_Items!$C:$C,0)),""))</x:f>
       </x:c>
       <x:c r="J18" s="16"/>
       <x:c r="K18" s="31"/>
@@ -1803,11 +1873,11 @@
       <x:formula1>"Sunny,Cloudy,Light Rain,Normal Rain,Heavy Rain,Snow"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="Item Description" prompt="Choose a description from the IDOT pay-item list, or type it manually." sqref="D13:D18">
-      <x:formula1>IDOT_Pay_Items!$C$2:$C$501</x:formula1>
+      <x:formula1>IDOT_Pay_Items!$C$2:$C$1000</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce8d80d43cd04085"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb480ab6bd704e79"/>
 </x:worksheet>
 </file>
 
@@ -1820,7 +1890,7 @@
     <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1850,7 +1920,7 @@
       <x:c r="D2" s="68"/>
       <x:c r="E2" s="68"/>
       <x:c r="G2" s="68" t="str">
-        <x:v>The app fills A:E with IDOT pay items. IDR_Form uses A for item-code dropdowns and C for description dropdowns.</x:v>
+        <x:v>The app fills A:E with IDOT pay items. On IDR_Form, select an item description in D13:D18; B fills item code and I fills unit. Custom descriptions will leave B/I blank unless the app fills them before download.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
